--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -1227,25 +1227,25 @@
         <v>46266</v>
       </c>
       <c r="B34" t="n">
-        <v>6918</v>
+        <v>6917</v>
       </c>
       <c r="C34" t="n">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="D34" t="n">
-        <v>6991621</v>
+        <v>6989996</v>
       </c>
       <c r="E34" t="n">
-        <v>1010.641948540041</v>
+        <v>1010.55312996964</v>
       </c>
       <c r="F34" t="n">
-        <v>9.757258448357931</v>
+        <v>9.741392987466281</v>
       </c>
       <c r="G34" t="n">
-        <v>8.826479438314937</v>
+        <v>8.625877632898703</v>
       </c>
       <c r="H34" t="n">
-        <v>19.17396984864666</v>
+        <v>19.14627130763533</v>
       </c>
     </row>
   </sheetData>

--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -1227,25 +1227,25 @@
         <v>46266</v>
       </c>
       <c r="B34" t="n">
-        <v>6917</v>
+        <v>6919</v>
       </c>
       <c r="C34" t="n">
-        <v>1083</v>
+        <v>1087</v>
       </c>
       <c r="D34" t="n">
-        <v>6989996</v>
+        <v>6998947</v>
       </c>
       <c r="E34" t="n">
-        <v>1010.55312996964</v>
+        <v>1011.554704437057</v>
       </c>
       <c r="F34" t="n">
-        <v>9.741392987466281</v>
+        <v>9.773123909249559</v>
       </c>
       <c r="G34" t="n">
-        <v>8.625877632898703</v>
+        <v>9.027081243731194</v>
       </c>
       <c r="H34" t="n">
-        <v>19.14627130763533</v>
+        <v>19.29884339415364</v>
       </c>
     </row>
   </sheetData>

--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -1227,25 +1227,25 @@
         <v>46266</v>
       </c>
       <c r="B34" t="n">
-        <v>6919</v>
+        <v>6922</v>
       </c>
       <c r="C34" t="n">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="D34" t="n">
-        <v>6998947</v>
+        <v>7004896</v>
       </c>
       <c r="E34" t="n">
-        <v>1011.554704437057</v>
+        <v>1011.975729557931</v>
       </c>
       <c r="F34" t="n">
-        <v>9.773123909249559</v>
+        <v>9.82072029192449</v>
       </c>
       <c r="G34" t="n">
-        <v>9.027081243731194</v>
+        <v>9.127382146439311</v>
       </c>
       <c r="H34" t="n">
-        <v>19.29884339415364</v>
+        <v>19.40024562213907</v>
       </c>
     </row>
   </sheetData>

--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -1227,25 +1227,25 @@
         <v>46266</v>
       </c>
       <c r="B34" t="n">
-        <v>6922</v>
+        <v>6924</v>
       </c>
       <c r="C34" t="n">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="D34" t="n">
-        <v>7004896</v>
+        <v>7009356</v>
       </c>
       <c r="E34" t="n">
-        <v>1011.975729557931</v>
+        <v>1012.327556325823</v>
       </c>
       <c r="F34" t="n">
-        <v>9.82072029192449</v>
+        <v>9.85245121370777</v>
       </c>
       <c r="G34" t="n">
-        <v>9.127382146439311</v>
+        <v>9.327983951855568</v>
       </c>
       <c r="H34" t="n">
-        <v>19.40024562213907</v>
+        <v>19.4762674639301</v>
       </c>
     </row>
   </sheetData>

--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -1227,25 +1227,25 @@
         <v>46266</v>
       </c>
       <c r="B34" t="n">
-        <v>6924</v>
+        <v>6923</v>
       </c>
       <c r="C34" t="n">
         <v>1090</v>
       </c>
       <c r="D34" t="n">
-        <v>7009356</v>
+        <v>7012212</v>
       </c>
       <c r="E34" t="n">
-        <v>1012.327556325823</v>
+        <v>1012.886320959122</v>
       </c>
       <c r="F34" t="n">
-        <v>9.85245121370777</v>
+        <v>9.836585752816118</v>
       </c>
       <c r="G34" t="n">
         <v>9.327983951855568</v>
       </c>
       <c r="H34" t="n">
-        <v>19.4762674639301</v>
+        <v>19.52494871508599</v>
       </c>
     </row>
   </sheetData>

--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -1227,25 +1227,25 @@
         <v>46266</v>
       </c>
       <c r="B34" t="n">
-        <v>6923</v>
+        <v>6920</v>
       </c>
       <c r="C34" t="n">
-        <v>1090</v>
+        <v>1086</v>
       </c>
       <c r="D34" t="n">
-        <v>7012212</v>
+        <v>7013979</v>
       </c>
       <c r="E34" t="n">
-        <v>1012.886320959122</v>
+        <v>1013.580780346821</v>
       </c>
       <c r="F34" t="n">
-        <v>9.836585752816118</v>
+        <v>9.788989370141209</v>
       </c>
       <c r="G34" t="n">
-        <v>9.327983951855568</v>
+        <v>8.926780341023077</v>
       </c>
       <c r="H34" t="n">
-        <v>19.52494871508599</v>
+        <v>19.5550676824503</v>
       </c>
     </row>
   </sheetData>

--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -1233,10 +1233,10 @@
         <v>1086</v>
       </c>
       <c r="D34" t="n">
-        <v>7013979</v>
+        <v>7014425</v>
       </c>
       <c r="E34" t="n">
-        <v>1013.580780346821</v>
+        <v>1013.645231213873</v>
       </c>
       <c r="F34" t="n">
         <v>9.788989370141209</v>
@@ -1245,7 +1245,7 @@
         <v>8.926780341023077</v>
       </c>
       <c r="H34" t="n">
-        <v>19.5550676824503</v>
+        <v>19.5626698666294</v>
       </c>
     </row>
   </sheetData>

--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -1233,10 +1233,10 @@
         <v>1086</v>
       </c>
       <c r="D34" t="n">
-        <v>7014425</v>
+        <v>7013817</v>
       </c>
       <c r="E34" t="n">
-        <v>1013.645231213873</v>
+        <v>1013.557369942196</v>
       </c>
       <c r="F34" t="n">
         <v>9.788989370141209</v>
@@ -1245,7 +1245,7 @@
         <v>8.926780341023077</v>
       </c>
       <c r="H34" t="n">
-        <v>19.5626698666294</v>
+        <v>19.55230635097715</v>
       </c>
     </row>
   </sheetData>

--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -1227,25 +1227,25 @@
         <v>46266</v>
       </c>
       <c r="B34" t="n">
-        <v>6920</v>
+        <v>6922</v>
       </c>
       <c r="C34" t="n">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="D34" t="n">
-        <v>7013817</v>
+        <v>7018648</v>
       </c>
       <c r="E34" t="n">
-        <v>1013.557369942196</v>
+        <v>1013.96243860156</v>
       </c>
       <c r="F34" t="n">
-        <v>9.788989370141209</v>
+        <v>9.82072029192449</v>
       </c>
       <c r="G34" t="n">
-        <v>8.926780341023077</v>
+        <v>9.027081243731194</v>
       </c>
       <c r="H34" t="n">
-        <v>19.55230635097715</v>
+        <v>19.63465198274679</v>
       </c>
     </row>
   </sheetData>

--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -1227,25 +1227,25 @@
         <v>46266</v>
       </c>
       <c r="B34" t="n">
-        <v>6922</v>
+        <v>6925</v>
       </c>
       <c r="C34" t="n">
-        <v>1087</v>
+        <v>1090</v>
       </c>
       <c r="D34" t="n">
-        <v>7018648</v>
+        <v>7026869</v>
       </c>
       <c r="E34" t="n">
-        <v>1013.96243860156</v>
+        <v>1014.710324909747</v>
       </c>
       <c r="F34" t="n">
-        <v>9.82072029192449</v>
+        <v>9.868316674599399</v>
       </c>
       <c r="G34" t="n">
-        <v>9.027081243731194</v>
+        <v>9.327983951855568</v>
       </c>
       <c r="H34" t="n">
-        <v>19.63465198274679</v>
+        <v>19.77478103238002</v>
       </c>
     </row>
   </sheetData>

--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -1227,25 +1227,25 @@
         <v>46266</v>
       </c>
       <c r="B34" t="n">
-        <v>6925</v>
+        <v>6926</v>
       </c>
       <c r="C34" t="n">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="D34" t="n">
-        <v>7026869</v>
+        <v>7033878</v>
       </c>
       <c r="E34" t="n">
-        <v>1014.710324909747</v>
+        <v>1015.575801328328</v>
       </c>
       <c r="F34" t="n">
-        <v>9.868316674599399</v>
+        <v>9.884182135491027</v>
       </c>
       <c r="G34" t="n">
-        <v>9.327983951855568</v>
+        <v>9.127382146439311</v>
       </c>
       <c r="H34" t="n">
-        <v>19.77478103238002</v>
+        <v>19.89425123173281</v>
       </c>
     </row>
   </sheetData>

--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -1227,25 +1227,25 @@
         <v>46266</v>
       </c>
       <c r="B34" t="n">
-        <v>6926</v>
+        <v>6927</v>
       </c>
       <c r="C34" t="n">
         <v>1088</v>
       </c>
       <c r="D34" t="n">
-        <v>7033878</v>
+        <v>7034953</v>
       </c>
       <c r="E34" t="n">
-        <v>1015.575801328328</v>
+        <v>1015.584379962466</v>
       </c>
       <c r="F34" t="n">
-        <v>9.884182135491027</v>
+        <v>9.900047596382677</v>
       </c>
       <c r="G34" t="n">
         <v>9.127382146439311</v>
       </c>
       <c r="H34" t="n">
-        <v>19.89425123173281</v>
+        <v>19.91257488194029</v>
       </c>
     </row>
   </sheetData>

--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -1227,25 +1227,25 @@
         <v>46266</v>
       </c>
       <c r="B34" t="n">
-        <v>6927</v>
+        <v>6926</v>
       </c>
       <c r="C34" t="n">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="D34" t="n">
-        <v>7034953</v>
+        <v>7035777</v>
       </c>
       <c r="E34" t="n">
-        <v>1015.584379962466</v>
+        <v>1015.849985561652</v>
       </c>
       <c r="F34" t="n">
-        <v>9.900047596382677</v>
+        <v>9.884182135491027</v>
       </c>
       <c r="G34" t="n">
-        <v>9.127382146439311</v>
+        <v>9.027081243731194</v>
       </c>
       <c r="H34" t="n">
-        <v>19.91257488194029</v>
+        <v>19.92662017289004</v>
       </c>
     </row>
   </sheetData>

--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -1227,25 +1227,25 @@
         <v>46266</v>
       </c>
       <c r="B34" t="n">
-        <v>6926</v>
+        <v>6924</v>
       </c>
       <c r="C34" t="n">
         <v>1087</v>
       </c>
       <c r="D34" t="n">
-        <v>7035777</v>
+        <v>7035429</v>
       </c>
       <c r="E34" t="n">
-        <v>1015.849985561652</v>
+        <v>1016.093154246101</v>
       </c>
       <c r="F34" t="n">
-        <v>9.884182135491027</v>
+        <v>9.85245121370777</v>
       </c>
       <c r="G34" t="n">
         <v>9.027081243731194</v>
       </c>
       <c r="H34" t="n">
-        <v>19.92662017289004</v>
+        <v>19.92068842379961</v>
       </c>
     </row>
   </sheetData>

--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -1230,22 +1230,22 @@
         <v>6924</v>
       </c>
       <c r="C34" t="n">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="D34" t="n">
-        <v>7035429</v>
+        <v>7035178</v>
       </c>
       <c r="E34" t="n">
-        <v>1016.093154246101</v>
+        <v>1016.056903523975</v>
       </c>
       <c r="F34" t="n">
         <v>9.85245121370777</v>
       </c>
       <c r="G34" t="n">
-        <v>9.027081243731194</v>
+        <v>9.127382146439311</v>
       </c>
       <c r="H34" t="n">
-        <v>19.92068842379961</v>
+        <v>19.91641006454186</v>
       </c>
     </row>
   </sheetData>

--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -1227,25 +1227,25 @@
         <v>46266</v>
       </c>
       <c r="B34" t="n">
-        <v>6924</v>
+        <v>6927</v>
       </c>
       <c r="C34" t="n">
         <v>1088</v>
       </c>
       <c r="D34" t="n">
-        <v>7035178</v>
+        <v>7037332</v>
       </c>
       <c r="E34" t="n">
-        <v>1016.056903523975</v>
+        <v>1015.927818680525</v>
       </c>
       <c r="F34" t="n">
-        <v>9.85245121370777</v>
+        <v>9.900047596382677</v>
       </c>
       <c r="G34" t="n">
         <v>9.127382146439311</v>
       </c>
       <c r="H34" t="n">
-        <v>19.91641006454186</v>
+        <v>19.95312554598085</v>
       </c>
     </row>
   </sheetData>

--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -1227,25 +1227,25 @@
         <v>46266</v>
       </c>
       <c r="B34" t="n">
-        <v>6927</v>
+        <v>6931</v>
       </c>
       <c r="C34" t="n">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="D34" t="n">
-        <v>7037332</v>
+        <v>7043230</v>
       </c>
       <c r="E34" t="n">
-        <v>1015.927818680525</v>
+        <v>1016.192468619247</v>
       </c>
       <c r="F34" t="n">
-        <v>9.900047596382677</v>
+        <v>9.963509439949236</v>
       </c>
       <c r="G34" t="n">
-        <v>9.127382146439311</v>
+        <v>9.327983951855568</v>
       </c>
       <c r="H34" t="n">
-        <v>19.95312554598085</v>
+        <v>20.05365846590992</v>
       </c>
     </row>
   </sheetData>

--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1248,6 +1248,32 @@
         <v>20.05365846590992</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B35" t="n">
+        <v>6930</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1089</v>
+      </c>
+      <c r="D35" t="n">
+        <v>7047753</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1016.991774891775</v>
+      </c>
+      <c r="F35" t="n">
+        <v>9.54789756560228</v>
+      </c>
+      <c r="G35" t="n">
+        <v>8.791208791208781</v>
+      </c>
+      <c r="H35" t="n">
+        <v>18.94239158868252</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -1259,10 +1259,10 @@
         <v>1089</v>
       </c>
       <c r="D35" t="n">
-        <v>7047753</v>
+        <v>7052661</v>
       </c>
       <c r="E35" t="n">
-        <v>1016.991774891775</v>
+        <v>1017.7</v>
       </c>
       <c r="F35" t="n">
         <v>9.54789756560228</v>
@@ -1271,7 +1271,7 @@
         <v>8.791208791208781</v>
       </c>
       <c r="H35" t="n">
-        <v>18.94239158868252</v>
+        <v>19.02522213877662</v>
       </c>
     </row>
   </sheetData>

--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -1259,10 +1259,10 @@
         <v>1089</v>
       </c>
       <c r="D35" t="n">
-        <v>7052661</v>
+        <v>7056980</v>
       </c>
       <c r="E35" t="n">
-        <v>1017.7</v>
+        <v>1018.323232323232</v>
       </c>
       <c r="F35" t="n">
         <v>9.54789756560228</v>
@@ -1271,7 +1271,7 @@
         <v>8.791208791208781</v>
       </c>
       <c r="H35" t="n">
-        <v>19.02522213877662</v>
+        <v>19.09811234779379</v>
       </c>
     </row>
   </sheetData>

--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -1253,25 +1253,25 @@
         <v>46296</v>
       </c>
       <c r="B35" t="n">
-        <v>6930</v>
+        <v>6929</v>
       </c>
       <c r="C35" t="n">
         <v>1089</v>
       </c>
       <c r="D35" t="n">
-        <v>7056980</v>
+        <v>7056909</v>
       </c>
       <c r="E35" t="n">
-        <v>1018.323232323232</v>
+        <v>1018.45995093087</v>
       </c>
       <c r="F35" t="n">
-        <v>9.54789756560228</v>
+        <v>9.53208978817579</v>
       </c>
       <c r="G35" t="n">
         <v>8.791208791208781</v>
       </c>
       <c r="H35" t="n">
-        <v>19.09811234779379</v>
+        <v>19.09691410633971</v>
       </c>
     </row>
   </sheetData>

--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -1253,25 +1253,25 @@
         <v>46296</v>
       </c>
       <c r="B35" t="n">
-        <v>6929</v>
+        <v>6928</v>
       </c>
       <c r="C35" t="n">
         <v>1089</v>
       </c>
       <c r="D35" t="n">
-        <v>7056909</v>
+        <v>7058267</v>
       </c>
       <c r="E35" t="n">
-        <v>1018.45995093087</v>
+        <v>1018.802973441109</v>
       </c>
       <c r="F35" t="n">
-        <v>9.53208978817579</v>
+        <v>9.5162820107493</v>
       </c>
       <c r="G35" t="n">
         <v>8.791208791208781</v>
       </c>
       <c r="H35" t="n">
-        <v>19.09691410633971</v>
+        <v>19.11983258372922</v>
       </c>
     </row>
   </sheetData>

--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -1253,25 +1253,25 @@
         <v>46296</v>
       </c>
       <c r="B35" t="n">
-        <v>6928</v>
+        <v>6931</v>
       </c>
       <c r="C35" t="n">
-        <v>1089</v>
+        <v>1094</v>
       </c>
       <c r="D35" t="n">
-        <v>7058267</v>
+        <v>7059207</v>
       </c>
       <c r="E35" t="n">
-        <v>1018.802973441109</v>
+        <v>1018.497619391141</v>
       </c>
       <c r="F35" t="n">
-        <v>9.5162820107493</v>
+        <v>9.563705343028772</v>
       </c>
       <c r="G35" t="n">
-        <v>8.791208791208781</v>
+        <v>9.290709290709298</v>
       </c>
       <c r="H35" t="n">
-        <v>19.11983258372922</v>
+        <v>19.1356966255158</v>
       </c>
     </row>
   </sheetData>

--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -1253,25 +1253,25 @@
         <v>46296</v>
       </c>
       <c r="B35" t="n">
-        <v>6931</v>
+        <v>6935</v>
       </c>
       <c r="C35" t="n">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="D35" t="n">
-        <v>7059207</v>
+        <v>7060578</v>
       </c>
       <c r="E35" t="n">
-        <v>1018.497619391141</v>
+        <v>1018.107858687815</v>
       </c>
       <c r="F35" t="n">
-        <v>9.563705343028772</v>
+        <v>9.626936452734736</v>
       </c>
       <c r="G35" t="n">
-        <v>9.290709290709298</v>
+        <v>9.490509490509492</v>
       </c>
       <c r="H35" t="n">
-        <v>19.1356966255158</v>
+        <v>19.15883449922788</v>
       </c>
     </row>
   </sheetData>

--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -1253,25 +1253,25 @@
         <v>46296</v>
       </c>
       <c r="B35" t="n">
-        <v>6935</v>
+        <v>6937</v>
       </c>
       <c r="C35" t="n">
         <v>1096</v>
       </c>
       <c r="D35" t="n">
-        <v>7060578</v>
+        <v>7064448</v>
       </c>
       <c r="E35" t="n">
-        <v>1018.107858687815</v>
+        <v>1018.37220700591</v>
       </c>
       <c r="F35" t="n">
-        <v>9.626936452734736</v>
+        <v>9.65855200758774</v>
       </c>
       <c r="G35" t="n">
         <v>9.490509490509492</v>
       </c>
       <c r="H35" t="n">
-        <v>19.15883449922788</v>
+        <v>19.22414709679596</v>
       </c>
     </row>
   </sheetData>

--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -1253,25 +1253,25 @@
         <v>46296</v>
       </c>
       <c r="B35" t="n">
-        <v>6937</v>
+        <v>6940</v>
       </c>
       <c r="C35" t="n">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="D35" t="n">
-        <v>7064448</v>
+        <v>7068167</v>
       </c>
       <c r="E35" t="n">
-        <v>1018.37220700591</v>
+        <v>1018.467867435158</v>
       </c>
       <c r="F35" t="n">
-        <v>9.65855200758774</v>
+        <v>9.705975339867212</v>
       </c>
       <c r="G35" t="n">
-        <v>9.490509490509492</v>
+        <v>9.690309690309684</v>
       </c>
       <c r="H35" t="n">
-        <v>19.22414709679596</v>
+        <v>19.28691132169407</v>
       </c>
     </row>
   </sheetData>

--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -1253,25 +1253,25 @@
         <v>46296</v>
       </c>
       <c r="B35" t="n">
-        <v>6940</v>
+        <v>6943</v>
       </c>
       <c r="C35" t="n">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="D35" t="n">
-        <v>7068167</v>
+        <v>7069707</v>
       </c>
       <c r="E35" t="n">
-        <v>1018.467867435158</v>
+        <v>1018.249603917615</v>
       </c>
       <c r="F35" t="n">
-        <v>9.705975339867212</v>
+        <v>9.753398672146707</v>
       </c>
       <c r="G35" t="n">
-        <v>9.690309690309684</v>
+        <v>9.790209790209792</v>
       </c>
       <c r="H35" t="n">
-        <v>19.28691132169407</v>
+        <v>19.31290134759971</v>
       </c>
     </row>
   </sheetData>

--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -1253,25 +1253,25 @@
         <v>46296</v>
       </c>
       <c r="B35" t="n">
-        <v>6943</v>
+        <v>6941</v>
       </c>
       <c r="C35" t="n">
-        <v>1099</v>
+        <v>1094</v>
       </c>
       <c r="D35" t="n">
-        <v>7069707</v>
+        <v>7069400</v>
       </c>
       <c r="E35" t="n">
-        <v>1018.249603917615</v>
+        <v>1018.498775392595</v>
       </c>
       <c r="F35" t="n">
-        <v>9.753398672146707</v>
+        <v>9.721783117293704</v>
       </c>
       <c r="G35" t="n">
-        <v>9.790209790209792</v>
+        <v>9.290709290709298</v>
       </c>
       <c r="H35" t="n">
-        <v>19.31290134759971</v>
+        <v>19.3077202190588</v>
       </c>
     </row>
   </sheetData>

--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -1259,10 +1259,10 @@
         <v>1094</v>
       </c>
       <c r="D35" t="n">
-        <v>7069400</v>
+        <v>7068301</v>
       </c>
       <c r="E35" t="n">
-        <v>1018.498775392595</v>
+        <v>1018.340440858666</v>
       </c>
       <c r="F35" t="n">
         <v>9.721783117293704</v>
@@ -1271,7 +1271,7 @@
         <v>9.290709290709298</v>
       </c>
       <c r="H35" t="n">
-        <v>19.3077202190588</v>
+        <v>19.28917279148068</v>
       </c>
     </row>
   </sheetData>

--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -1256,22 +1256,22 @@
         <v>6941</v>
       </c>
       <c r="C35" t="n">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="D35" t="n">
-        <v>7068301</v>
+        <v>7069666</v>
       </c>
       <c r="E35" t="n">
-        <v>1018.340440858666</v>
+        <v>1018.537098400807</v>
       </c>
       <c r="F35" t="n">
         <v>9.721783117293704</v>
       </c>
       <c r="G35" t="n">
-        <v>9.290709290709298</v>
+        <v>9.490509490509492</v>
       </c>
       <c r="H35" t="n">
-        <v>19.28917279148068</v>
+        <v>19.31220940535159</v>
       </c>
     </row>
   </sheetData>

--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -1253,25 +1253,25 @@
         <v>46296</v>
       </c>
       <c r="B35" t="n">
-        <v>6941</v>
+        <v>6947</v>
       </c>
       <c r="C35" t="n">
         <v>1096</v>
       </c>
       <c r="D35" t="n">
-        <v>7069666</v>
+        <v>7071373</v>
       </c>
       <c r="E35" t="n">
-        <v>1018.537098400807</v>
+        <v>1017.903123650497</v>
       </c>
       <c r="F35" t="n">
-        <v>9.721783117293704</v>
+        <v>9.81662978185267</v>
       </c>
       <c r="G35" t="n">
         <v>9.490509490509492</v>
       </c>
       <c r="H35" t="n">
-        <v>19.31220940535159</v>
+        <v>19.34101783017037</v>
       </c>
     </row>
   </sheetData>

--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -1253,25 +1253,25 @@
         <v>46296</v>
       </c>
       <c r="B35" t="n">
-        <v>6947</v>
+        <v>6951</v>
       </c>
       <c r="C35" t="n">
-        <v>1096</v>
+        <v>1099</v>
       </c>
       <c r="D35" t="n">
-        <v>7071373</v>
+        <v>7075688</v>
       </c>
       <c r="E35" t="n">
-        <v>1017.903123650497</v>
+        <v>1017.938138397353</v>
       </c>
       <c r="F35" t="n">
-        <v>9.81662978185267</v>
+        <v>9.879860891558657</v>
       </c>
       <c r="G35" t="n">
-        <v>9.490509490509492</v>
+        <v>9.790209790209792</v>
       </c>
       <c r="H35" t="n">
-        <v>19.34101783017037</v>
+        <v>19.41384053262676</v>
       </c>
     </row>
   </sheetData>

--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -1253,25 +1253,25 @@
         <v>46296</v>
       </c>
       <c r="B35" t="n">
-        <v>6951</v>
+        <v>6956</v>
       </c>
       <c r="C35" t="n">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="D35" t="n">
-        <v>7075688</v>
+        <v>7078819</v>
       </c>
       <c r="E35" t="n">
-        <v>1017.938138397353</v>
+        <v>1017.656555491662</v>
       </c>
       <c r="F35" t="n">
-        <v>9.879860891558657</v>
+        <v>9.95889977869111</v>
       </c>
       <c r="G35" t="n">
-        <v>9.790209790209792</v>
+        <v>9.990009990009984</v>
       </c>
       <c r="H35" t="n">
-        <v>19.41384053262676</v>
+        <v>19.46668129308817</v>
       </c>
     </row>
   </sheetData>

--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -1253,25 +1253,25 @@
         <v>46296</v>
       </c>
       <c r="B35" t="n">
-        <v>6956</v>
+        <v>6958</v>
       </c>
       <c r="C35" t="n">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="D35" t="n">
-        <v>7078819</v>
+        <v>7078356</v>
       </c>
       <c r="E35" t="n">
-        <v>1017.656555491662</v>
+        <v>1017.297499281403</v>
       </c>
       <c r="F35" t="n">
-        <v>9.95889977869111</v>
+        <v>9.990515333544113</v>
       </c>
       <c r="G35" t="n">
-        <v>9.990009990009984</v>
+        <v>9.690309690309684</v>
       </c>
       <c r="H35" t="n">
-        <v>19.46668129308817</v>
+        <v>19.45886740867628</v>
       </c>
     </row>
   </sheetData>

--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -1259,10 +1259,10 @@
         <v>1098</v>
       </c>
       <c r="D35" t="n">
-        <v>7078356</v>
+        <v>7077958</v>
       </c>
       <c r="E35" t="n">
-        <v>1017.297499281403</v>
+        <v>1017.240298936476</v>
       </c>
       <c r="F35" t="n">
         <v>9.990515333544113</v>
@@ -1271,7 +1271,7 @@
         <v>9.690309690309684</v>
       </c>
       <c r="H35" t="n">
-        <v>19.45886740867628</v>
+        <v>19.4521505058773</v>
       </c>
     </row>
   </sheetData>

--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -1256,22 +1256,22 @@
         <v>6958</v>
       </c>
       <c r="C35" t="n">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="D35" t="n">
-        <v>7077958</v>
+        <v>7077877</v>
       </c>
       <c r="E35" t="n">
-        <v>1017.240298936476</v>
+        <v>1017.228657660247</v>
       </c>
       <c r="F35" t="n">
         <v>9.990515333544113</v>
       </c>
       <c r="G35" t="n">
-        <v>9.690309690309684</v>
+        <v>9.790209790209792</v>
       </c>
       <c r="H35" t="n">
-        <v>19.4521505058773</v>
+        <v>19.45078349802121</v>
       </c>
     </row>
   </sheetData>

--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -1253,25 +1253,25 @@
         <v>46296</v>
       </c>
       <c r="B35" t="n">
-        <v>6958</v>
+        <v>6962</v>
       </c>
       <c r="C35" t="n">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="D35" t="n">
-        <v>7077877</v>
+        <v>7079424</v>
       </c>
       <c r="E35" t="n">
-        <v>1017.228657660247</v>
+        <v>1016.866417696064</v>
       </c>
       <c r="F35" t="n">
-        <v>9.990515333544113</v>
+        <v>10.05374644325008</v>
       </c>
       <c r="G35" t="n">
-        <v>9.790209790209792</v>
+        <v>9.990009990009984</v>
       </c>
       <c r="H35" t="n">
-        <v>19.45078349802121</v>
+        <v>19.47689166040825</v>
       </c>
     </row>
   </sheetData>

--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -1253,25 +1253,25 @@
         <v>46296</v>
       </c>
       <c r="B35" t="n">
-        <v>6962</v>
+        <v>6966</v>
       </c>
       <c r="C35" t="n">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="D35" t="n">
-        <v>7079424</v>
+        <v>7084773</v>
       </c>
       <c r="E35" t="n">
-        <v>1016.866417696064</v>
+        <v>1017.050387596899</v>
       </c>
       <c r="F35" t="n">
-        <v>10.05374644325008</v>
+        <v>10.11697755295606</v>
       </c>
       <c r="G35" t="n">
-        <v>9.990009990009984</v>
+        <v>10.08991008991009</v>
       </c>
       <c r="H35" t="n">
-        <v>19.47689166040825</v>
+        <v>19.56716480882985</v>
       </c>
     </row>
   </sheetData>

--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -1256,22 +1256,22 @@
         <v>6966</v>
       </c>
       <c r="C35" t="n">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="D35" t="n">
-        <v>7084773</v>
+        <v>7088610</v>
       </c>
       <c r="E35" t="n">
-        <v>1017.050387596899</v>
+        <v>1017.60120585702</v>
       </c>
       <c r="F35" t="n">
         <v>10.11697755295606</v>
       </c>
       <c r="G35" t="n">
-        <v>10.08991008991009</v>
+        <v>10.1898101898102</v>
       </c>
       <c r="H35" t="n">
-        <v>19.56716480882985</v>
+        <v>19.63192047727138</v>
       </c>
     </row>
   </sheetData>

--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -1256,22 +1256,22 @@
         <v>6966</v>
       </c>
       <c r="C35" t="n">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="D35" t="n">
-        <v>7088610</v>
+        <v>7092323</v>
       </c>
       <c r="E35" t="n">
-        <v>1017.60120585702</v>
+        <v>1018.134223370657</v>
       </c>
       <c r="F35" t="n">
         <v>10.11697755295606</v>
       </c>
       <c r="G35" t="n">
-        <v>10.1898101898102</v>
+        <v>10.38961038961039</v>
       </c>
       <c r="H35" t="n">
-        <v>19.63192047727138</v>
+        <v>19.69458344232831</v>
       </c>
     </row>
   </sheetData>

--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -1253,25 +1253,25 @@
         <v>46296</v>
       </c>
       <c r="B35" t="n">
-        <v>6966</v>
+        <v>6967</v>
       </c>
       <c r="C35" t="n">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D35" t="n">
-        <v>7092323</v>
+        <v>7091982</v>
       </c>
       <c r="E35" t="n">
-        <v>1018.134223370657</v>
+        <v>1017.939141667863</v>
       </c>
       <c r="F35" t="n">
-        <v>10.11697755295606</v>
+        <v>10.13278533038255</v>
       </c>
       <c r="G35" t="n">
-        <v>10.38961038961039</v>
+        <v>10.68931068931069</v>
       </c>
       <c r="H35" t="n">
-        <v>19.69458344232831</v>
+        <v>19.68882850802063</v>
       </c>
     </row>
   </sheetData>

--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -1259,10 +1259,10 @@
         <v>1108</v>
       </c>
       <c r="D35" t="n">
-        <v>7091982</v>
+        <v>7091857</v>
       </c>
       <c r="E35" t="n">
-        <v>1017.939141667863</v>
+        <v>1017.921199942586</v>
       </c>
       <c r="F35" t="n">
         <v>10.13278533038255</v>
@@ -1271,7 +1271,7 @@
         <v>10.68931068931069</v>
       </c>
       <c r="H35" t="n">
-        <v>19.68882850802063</v>
+        <v>19.68671892799581</v>
       </c>
     </row>
   </sheetData>

--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -1259,10 +1259,10 @@
         <v>1108</v>
       </c>
       <c r="D35" t="n">
-        <v>7091857</v>
+        <v>7091204</v>
       </c>
       <c r="E35" t="n">
-        <v>1017.921199942586</v>
+        <v>1017.827472369743</v>
       </c>
       <c r="F35" t="n">
         <v>10.13278533038255</v>
@@ -1271,7 +1271,7 @@
         <v>10.68931068931069</v>
       </c>
       <c r="H35" t="n">
-        <v>19.68671892799581</v>
+        <v>19.67569848194621</v>
       </c>
     </row>
   </sheetData>

--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -1253,25 +1253,25 @@
         <v>46296</v>
       </c>
       <c r="B35" t="n">
-        <v>6967</v>
+        <v>6970</v>
       </c>
       <c r="C35" t="n">
-        <v>1108</v>
+        <v>1117</v>
       </c>
       <c r="D35" t="n">
-        <v>7091204</v>
+        <v>7091721</v>
       </c>
       <c r="E35" t="n">
-        <v>1017.827472369743</v>
+        <v>1017.463558106169</v>
       </c>
       <c r="F35" t="n">
-        <v>10.13278533038255</v>
+        <v>10.18020866266203</v>
       </c>
       <c r="G35" t="n">
-        <v>10.68931068931069</v>
+        <v>11.5884115884116</v>
       </c>
       <c r="H35" t="n">
-        <v>19.67569848194621</v>
+        <v>19.68442370492882</v>
       </c>
     </row>
   </sheetData>

--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -1253,25 +1253,25 @@
         <v>46296</v>
       </c>
       <c r="B35" t="n">
-        <v>6970</v>
+        <v>6971</v>
       </c>
       <c r="C35" t="n">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="D35" t="n">
-        <v>7091721</v>
+        <v>7095086</v>
       </c>
       <c r="E35" t="n">
-        <v>1017.463558106169</v>
+        <v>1017.800315593172</v>
       </c>
       <c r="F35" t="n">
-        <v>10.18020866266203</v>
+        <v>10.19601644008852</v>
       </c>
       <c r="G35" t="n">
-        <v>11.5884115884116</v>
+        <v>11.48851148851149</v>
       </c>
       <c r="H35" t="n">
-        <v>19.68442370492882</v>
+        <v>19.74121359919667</v>
       </c>
     </row>
   </sheetData>

--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -1256,22 +1256,22 @@
         <v>6971</v>
       </c>
       <c r="C35" t="n">
-        <v>1116</v>
+        <v>1112</v>
       </c>
       <c r="D35" t="n">
-        <v>7095086</v>
+        <v>7096892</v>
       </c>
       <c r="E35" t="n">
-        <v>1017.800315593172</v>
+        <v>1018.059388896858</v>
       </c>
       <c r="F35" t="n">
         <v>10.19601644008852</v>
       </c>
       <c r="G35" t="n">
-        <v>11.48851148851149</v>
+        <v>11.08891108891108</v>
       </c>
       <c r="H35" t="n">
-        <v>19.74121359919667</v>
+        <v>19.7716928113951</v>
       </c>
     </row>
   </sheetData>

--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -1253,25 +1253,25 @@
         <v>46296</v>
       </c>
       <c r="B35" t="n">
-        <v>6971</v>
+        <v>6975</v>
       </c>
       <c r="C35" t="n">
-        <v>1112</v>
+        <v>1107</v>
       </c>
       <c r="D35" t="n">
-        <v>7096892</v>
+        <v>7097769</v>
       </c>
       <c r="E35" t="n">
-        <v>1018.059388896858</v>
+        <v>1017.601290322581</v>
       </c>
       <c r="F35" t="n">
-        <v>10.19601644008852</v>
+        <v>10.2592475497945</v>
       </c>
       <c r="G35" t="n">
-        <v>11.08891108891108</v>
+        <v>10.58941058941059</v>
       </c>
       <c r="H35" t="n">
-        <v>19.7716928113951</v>
+        <v>19.78649362484916</v>
       </c>
     </row>
   </sheetData>

--- a/iserv_stats.xlsx
+++ b/iserv_stats.xlsx
@@ -1253,25 +1253,25 @@
         <v>46296</v>
       </c>
       <c r="B35" t="n">
-        <v>6975</v>
+        <v>6978</v>
       </c>
       <c r="C35" t="n">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="D35" t="n">
-        <v>7097769</v>
+        <v>7097866</v>
       </c>
       <c r="E35" t="n">
-        <v>1017.601290322581</v>
+        <v>1017.177701347091</v>
       </c>
       <c r="F35" t="n">
-        <v>10.2592475497945</v>
+        <v>10.30667088207398</v>
       </c>
       <c r="G35" t="n">
-        <v>10.58941058941059</v>
+        <v>10.78921078921078</v>
       </c>
       <c r="H35" t="n">
-        <v>19.78649362484916</v>
+        <v>19.78813065894842</v>
       </c>
     </row>
   </sheetData>
